--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50216D21-D353-4D8F-85C9-BAA5F66CBA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5FFC08-0E2D-4506-A7FA-288C5DF2C549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="324">
   <si>
     <t>s</t>
   </si>
@@ -1269,6 +1269,46 @@
   </si>
   <si>
     <t>A5358944E541450B08F65E4B276241D2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>息县文化图书馆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12411528MB0P16902D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F3D2B62FDFCCD2601EC65C78DF626306</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张云镛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>37万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助（财政补助收入）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>息县文化广电和旅游局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年08月14日 至 2026年08月13日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南省息县一桥西段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供文化艺术和图书借阅服务，促进社会经济文化发展。图书、文献、报刊、音像资料采编与储藏 图书资料借阅</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1663,7 +1703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -2869,6 +2909,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="35" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5FFC08-0E2D-4506-A7FA-288C5DF2C549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1B1F2E-9968-4C6E-8B34-B1E8FCAE9930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="333">
   <si>
     <t>s</t>
   </si>
@@ -1309,6 +1309,42 @@
   </si>
   <si>
     <t>提供文化艺术和图书借阅服务，促进社会经济文化发展。图书、文献、报刊、音像资料采编与储藏 图书资料借阅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新乡县翟坡镇第三中心小学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1241072109142617XX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>98DAA2F72D7E959D0C19561B66314FE5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新乡县教育体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>361.66万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>史利艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南省新乡县翟坡镇兴宁村</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实施小学义务教育，促进基础教育发展。　小学学历教育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年03月22日 至 2029年03月21日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1703,7 +1739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -2944,6 +2980,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="36" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1B1F2E-9968-4C6E-8B34-B1E8FCAE9930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F43569-2264-45D3-903B-56D29799681F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="343">
   <si>
     <t>s</t>
   </si>
@@ -1345,6 +1345,46 @@
   </si>
   <si>
     <t>自 2024年03月22日 至 2029年03月21日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南京航空航天大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12100000466006826U</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D11C9CD9B95E2907B339EF35F67C6CF0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏省南京市秦淮区御道街29号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等学历航空航天人才，促进科技发展。 力学、机械、控制、仪器仪表、电气、信息、计算机、交通运输、航空宇航、管理本科和硕士博士研究生学历教育 哲学、经济、政治、材料、能源动力、数学、工商管理、工业设计、计算机、电子、光学、土木本科和硕士研究生学历教育 法学、外语、经济、物理、化学、金融、市场营销、生物、会计本科学历教育 博士后培养 相关科研、继续教育、高职教育、专业培训与学术交流</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姜斌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助、事业、经营收入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30590万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工业和信息化部</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2021年10月28日 至 2026年10月28日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1739,7 +1779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -3015,6 +3055,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="37" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F43569-2264-45D3-903B-56D29799681F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D925A8DF-B0E7-40F5-A684-C45443ACCFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="353">
   <si>
     <t>s</t>
   </si>
@@ -1385,6 +1385,46 @@
   </si>
   <si>
     <t>自 2021年10月28日 至 2026年10月28日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广东省青少年事业发展中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12440000MB2C77360L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4E12E437B8ED607940710DAB49D947A3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负责团属新媒体矩阵建设、丰富青少年网络精神文化生活、参与清朗网络空间建设等工作；负责青少年网上服务平台建设、做好青少年大数据建设应用；承接联系、引领和服务各领域青年和各级青年社会组织的有关具体活动项目；筹集管理广东青少年发展基金；承担团省委交办的其他工作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广东省广州市越秀区寺贝通津1号之五101房</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李绍斌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （财政补助二类）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>共青团广东省委员会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年03月20日 至 2028年03月19日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1779,7 +1819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -3090,6 +3130,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="38" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D925A8DF-B0E7-40F5-A684-C45443ACCFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B5EB78-25DF-48F9-8E7C-B8C7395E8DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="363">
   <si>
     <t>s</t>
   </si>
@@ -1425,6 +1425,46 @@
   </si>
   <si>
     <t>自 2023年03月20日 至 2028年03月19日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宁波市体育发展中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123302004195296676</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D40119D3A337F3853F19BED30A2C292E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贯彻实施《体育强国纲要》,承担网球等运动项目的竞技体育任务。培养选拔高水平竞技体育后备人才，向省运动队和其他高层次体育训练单位输送优秀体育后备人才。组队参加相关运动项目的比赛。为各类全民健身、体育比赛、文艺活动、重大社会活动提供场所和相关服务。发展体育产业，开展体育培训及项目推广普及，传播体育文化。为体育信息化建设提供服务保障。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宁波市中兴路360号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李瑜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政适当补助 （差额财政补助）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38590万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宁波市体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年06月21日 至 2027年03月03日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1819,7 +1859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -3165,6 +3205,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="39" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B5EB78-25DF-48F9-8E7C-B8C7395E8DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D77F873-7ADA-4CD7-80D7-12F2C4FE4E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="373">
   <si>
     <t>s</t>
   </si>
@@ -1465,6 +1465,46 @@
   </si>
   <si>
     <t>自 2024年06月21日 至 2027年03月03日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苍梧县健康促进与教育中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12450421498774627T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A8EE937BE3EFB12BBB082ED4509E1641</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为人民在其整个人生实现并保持能获得的最高健康水平创造条件。使人民增加期望寿命和提高生活质量；在国家间和国家内部促进卫生公平；使人民获得可持续的卫生系统和服务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广西苍梧县龙圩镇城西大道13号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李杰华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （全额拨款）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苍梧县卫生健康局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年12月30日 至 2029年12月29日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1859,7 +1899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -3240,6 +3280,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="40" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D77F873-7ADA-4CD7-80D7-12F2C4FE4E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA028595-C506-4734-8BD8-056133312BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="382">
   <si>
     <t>s</t>
   </si>
@@ -1505,6 +1505,42 @@
   </si>
   <si>
     <t>自 2024年12月30日 至 2029年12月29日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>庆云县第二幼儿园</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12371423MB2321625Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3A9CEC6E52226A08692EB97E98F746EA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼儿园贯彻党中央、省委和德州市委关于教育工作的方针政策和决策部署，落实县委、县政府工作要求。负责3-6岁适龄儿童，为学龄前儿童提供保育和教育服务。负责3岁以下婴儿托育照护服务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山东省德州市庆云县文化路1695号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张韦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>270万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>庆云县教育和体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年09月11日 至 2026年03月31日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1899,7 +1935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -3315,6 +3351,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="41" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA028595-C506-4734-8BD8-056133312BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDA0C15-D1A0-4760-BABC-5F87EFB2CFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="392">
   <si>
     <t>s</t>
   </si>
@@ -1541,6 +1541,46 @@
   </si>
   <si>
     <t>自 2024年09月11日 至 2026年03月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桑植县河口乡敬老院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12430822058039856E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8F479656FBC4D6F19619D6B68CD2988D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龚德双</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>86万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桑植县河口乡人民政府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>该单位已注销</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桑植县河口乡河口村牌楼组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为农村五保对象提供养老服务。 农村五保对象养老服务 社会寄托养服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2020年04月30日 至 2025年40月30日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1935,7 +1975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -3386,6 +3426,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="42" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDA0C15-D1A0-4760-BABC-5F87EFB2CFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0655EBA-2A2A-4B22-AC37-FF2BD09B2D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="402">
   <si>
     <t>s</t>
   </si>
@@ -1580,7 +1580,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>自 2020年04月30日 至 2025年40月30日</t>
+    <t>自 2020年04月30日 至 2025年04月30日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>来凤县翔凤镇大沟小学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12422827F88241667P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0E55D773D65BF440F19D00F784E32683</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实施小学义务教育，促进基础教育发展。全面贯彻实施《教育法》和《义务教育法》普及九年义务教育。贯彻党的教育方针，培养合格人才。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>来凤县翔凤镇大沟管理区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>曾令昌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （财政拨款）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>来凤县教育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年04月28日 至 2030年04月27日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1975,7 +2015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -3461,6 +3501,41 @@
         <v>388</v>
       </c>
     </row>
+    <row r="43" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0655EBA-2A2A-4B22-AC37-FF2BD09B2D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD17527D-3043-44A6-9866-0A0235A65E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="411">
   <si>
     <t>s</t>
   </si>
@@ -1621,6 +1621,42 @@
   </si>
   <si>
     <t>自 2025年04月28日 至 2030年04月27日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>井冈山大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12360000492390024X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5A4ADED44FCC7CD2ABA527D6894A3A0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等学历人才，促进科技文化发展。文学、理学、医学等学科的专科、本科、研究生教育等学历教育，来华留学生教育、继续教育、专业培训，相关科学研究、学术交流及社会服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吉安市青原区学苑路28号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗旭彪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>129689.18万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江西省人民政府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年03月28日 至 2030年03月27日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2015,7 +2051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -3536,6 +3572,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="44" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD17527D-3043-44A6-9866-0A0235A65E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23834D2-A85F-467D-A85D-FDDD488E4929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="421">
   <si>
     <t>s</t>
   </si>
@@ -1657,6 +1657,46 @@
   </si>
   <si>
     <t>自 2025年03月28日 至 2030年03月27日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山东大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12100000495570303U</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等学历人才，促进科技文化发展。 哲学类、理学类、管理学类、经济学类、文学类、历史学类、法学类、工学类、医学类、教育学类学科高等专科、本科和研究生班学历教育 哲学类、理学类、管理学类、经济学类、文学类、历史学类、法学类、工学类、医学类学科硕士研究生和博士研究生学历教育 博士后培养 相关科学研究、继续教育、专业培训与学术交流</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山东省济南市山大南路27号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李术才</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助、事业、附属单位上缴收入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100402万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教育部</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2022年09月19日 至 2027年09月19日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7B1EA91BDD98F91F90D4BABBF3E8B600</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2051,7 +2091,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -3607,6 +3647,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="45" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23834D2-A85F-467D-A85D-FDDD488E4929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620ED372-5014-4AFE-8DEF-3A827F3A4B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="430">
   <si>
     <t>s</t>
   </si>
@@ -1697,6 +1697,42 @@
   </si>
   <si>
     <t>7B1EA91BDD98F91F90D4BABBF3E8B600</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怀化学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12430000448195678M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C57E471FFE1FDD7E0F78458503B3C621</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等学历人才，促进科技文化发展。 综合型本科学历教育 科学研究为主，结合继续教育 相关社会服务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怀化市鹤城区迎丰东路798号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>董正宇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90222.32万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖南省教育厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年03月17日 至 2028年03月17日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2091,7 +2127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -3682,6 +3718,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="46" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620ED372-5014-4AFE-8DEF-3A827F3A4B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C34B77C-B83C-4782-92CD-F501BC3DF063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="440">
   <si>
     <t>s</t>
   </si>
@@ -1733,6 +1733,46 @@
   </si>
   <si>
     <t>自 2023年03月17日 至 2028年03月17日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张家港市体育彩票管理中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123205824672308548</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7FFC132E57BB1B6520239B5603858071</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发展体育彩票事业，为彩民提供服务。做好体育彩票发行宣传 规划全市体育彩票销售站的布点 负责销售员队伍管理、销售员培训 体育彩票销售报表的汇总及上报 体育彩票较大金额中奖彩民的兑奖 负责彩票终端机的检查、验收、监督、维修保养</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张家港市暨阳中路132号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陆正霞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自收自支</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.14万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张家港市文体广电和旅游局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2022年03月07日 至 2027年03月07日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2127,7 +2167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -3753,6 +3793,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="47" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C34B77C-B83C-4782-92CD-F501BC3DF063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1847C242-DC8D-4FBE-99C7-8D2855955F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="449">
   <si>
     <t>s</t>
   </si>
@@ -1773,6 +1773,42 @@
   </si>
   <si>
     <t>自 2022年03月07日 至 2027年03月07日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖北城市建设职业技术学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>124200004200000741</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FD503536F6936B74FD43B879C671BA44</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高、中等学历技术应用人才，促进科技文化发展。培养中高级城乡建设技术和管理人才；建筑设计咨询。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武汉市藏龙大道28号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>董文斌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3026万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖北省住房和城乡建设厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年03月04日 至 2031年03月03日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2167,7 +2203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -3828,6 +3864,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="48" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1847C242-DC8D-4FBE-99C7-8D2855955F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF36D863-30CF-4393-9902-7CF4F9C99D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="475">
   <si>
     <t>s</t>
   </si>
@@ -1809,6 +1809,110 @@
   </si>
   <si>
     <t>自 2026年03月04日 至 2031年03月03日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>越西县卫生健康宣传教育促进中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上栗县卫生健康教育中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金阳县健康教育中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12513434MB1L389079</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A7502FF4DB0D0FB2D35DAF7236759D5D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组织开展艾滋病防治、计划生育、疫情防控等工作的宣传教育；负责公益性的卫生工作传播项目的策划、组织与实施，开展卫生健康社会倡导活动；开展健康素养与健康行为监测，并对健康素养与健康行为进行评估 发布相关信息；指导其他部门做好卫生健康宣传教育等工作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>越西县越城镇文民路3号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>殷国琼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>越西县卫生健康局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年02月21日 至 2028年02月21日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12360322058847386Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7CE8BA72B7DFC2A4773E0520B54853B3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划生育技术指导，避孕和节育的医学检查，避孕节育手术以及其它生殖保健服务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上栗县李畋大道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柳沅冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上栗县卫生健康委员会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年05月07日 至 2029年05月06日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12513430MB0T30425E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高全县卫生技术人员理论、业务知识水平，为全县人民健康服务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金阳县天地坝镇下南街23号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咪色里呷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金阳县卫生健康局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年03月17日 至 2030年03月16日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30601D3D3EFCE21FADF440146F108BDF</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2203,7 +2307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -3899,6 +4003,111 @@
         <v>30</v>
       </c>
     </row>
+    <row r="49" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF36D863-30CF-4393-9902-7CF4F9C99D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F27D29-4DD9-4564-B748-AADAB9CCF4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="484">
   <si>
     <t>s</t>
   </si>
@@ -1913,6 +1913,42 @@
   </si>
   <si>
     <t>30601D3D3EFCE21FADF440146F108BDF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒙阴县人民医院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12371328495296332P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03C7F356FE24FD579C6768EA5948DE15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为人民身体健康提供医疗与护理保健服务。医疗与护理、医学教学、医学研究、卫生医疗人员培训、卫生技术人员继续教育、保健与健康教育。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒙阴县东蒙路368号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孙晓庆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9304万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒙阴县卫生健康局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年03月25日 至 2027年03月31日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2307,7 +2343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -4108,6 +4144,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="52" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F27D29-4DD9-4564-B748-AADAB9CCF4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A68641-234E-4B4A-833E-1C6B72BCB033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="494">
   <si>
     <t>s</t>
   </si>
@@ -1949,6 +1949,46 @@
   </si>
   <si>
     <t>自 2026年03月25日 至 2027年03月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南工业贸易职业学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>124100004158031988</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CA2E2BB5C9133BCD81EF9B8EC19A1E6A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等专科学历技术应用人才，促进科技文化发展。 粮食工程、计算机应用技术、会计电算化、电子商务、机电一体化技术、汽车检测与维修、商务英语、室内设计技术、食品加工技术、物流管理、旅游英语、会计与审计学科高等专科学历教育 相关中专学历教育、成人中专学历教育　干部培训　相关技术开发与社会服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南省郑州市金水区优胜北路4号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>曹利强</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （财政补助收入、事业收入）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>56365万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南省教育厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年08月18日 至 2030年08月17日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2343,7 +2383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -4179,6 +4219,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="53" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A68641-234E-4B4A-833E-1C6B72BCB033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BCA4E2-CD2F-41B4-BCDC-2CCCE8D579E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="502">
   <si>
     <t>s</t>
   </si>
@@ -1989,6 +1989,38 @@
   </si>
   <si>
     <t>自 2025年08月18日 至 2030年08月17日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>皖西学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12340000486188663C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>56F3C8E9A42731A446DB2117985B9C23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等本科学历师资人才</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安徽省六安市河西</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>肖新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>67353.98万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年09月12日 至 2030年09月11日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2383,7 +2415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -4254,6 +4286,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="54" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BCA4E2-CD2F-41B4-BCDC-2CCCE8D579E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07962A09-1125-4404-B3D8-E5ABFBF16CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="510">
   <si>
     <t>s</t>
   </si>
@@ -2021,6 +2021,38 @@
   </si>
   <si>
     <t>自 2025年09月12日 至 2030年09月11日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B5AB6E096FAD361794D6CD173B2B2E71</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>景德镇陶瓷大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12360000491242441C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等学历人才、艺术人才，促进陶瓷科技与艺术发展。材料科学与工程、设计学等学科本科、硕士研究生、博士研究生学历教育及相关科学研究、继续教育、专业培训、学术交流、合作办学及相关社会服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江西省景德镇市浮梁县湘湖镇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吕品昌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>163536.4万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年04月06日 至 2028年04月06日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2415,7 +2447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -4321,6 +4353,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="55" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07962A09-1125-4404-B3D8-E5ABFBF16CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B20FD4-D72C-472E-95BC-84CA1373059C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="520">
   <si>
     <t>s</t>
   </si>
@@ -2053,6 +2053,46 @@
   </si>
   <si>
     <t>自 2023年04月06日 至 2028年04月06日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南京市第二医院（南京市公共卫生医疗中心、江苏省传染病医院）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1232010042580096XJ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>473CF6BF27E668258471A55264B50820</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为人民提供医疗与护理保健服务。传染科，肝病科，内、外、妇、儿科，肿瘤，老年病，皮肤科（性病专业）等医疗；承担高等院校医学教学，从事临床医学研究；卫生医疗人员培训、继续教育、保健与健康教育。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南京市钟阜路1－1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>殷国平</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>差额拨款 （差额拨款）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6612万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南京市卫生健康委员会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年02月21日 至 2030年02月21日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2447,7 +2487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -4388,6 +4428,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="56" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B20FD4-D72C-472E-95BC-84CA1373059C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CFDFEC-8A27-42F3-B5DB-175082AC5B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="530">
   <si>
     <t>s</t>
   </si>
@@ -2093,6 +2093,46 @@
   </si>
   <si>
     <t>自 2025年02月21日 至 2030年02月21日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑龙江农业职业技术学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12230800414277261N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04F6C906FFF18DE99FEA4E5A89D3E4D3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承担专科层次高等职业教育与中等职业教育工作；开展科学技术研究，并为社会提供相关服务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佳木斯市前进区胜利东路248号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韩雪松</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （财政部分补助）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26376万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑龙江省教育厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年01月16日 至 2029年01月15日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2487,7 +2527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -4463,6 +4503,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="57" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CFDFEC-8A27-42F3-B5DB-175082AC5B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EAA62E4-3CB5-4183-BB91-7595D00E1C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="548">
   <si>
     <t>s</t>
   </si>
@@ -2133,6 +2133,78 @@
   </si>
   <si>
     <t>自 2024年01月16日 至 2029年01月15日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兰州文理学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>126200004380023503</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2B1B8E3E272E9E9631C7B3457B251A83</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招收和培养多学科本科、专科类专业人才。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兰州市城关区雁滩北面滩400号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王顶明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>94930万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甘肃省教育厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年04月22日 至 2029年04月21日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广州医科大学附属肿瘤医院（广州市癌症防治中心）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12440100455350760C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21E8A2B0FE58DDC9CE6FFB2D5865020B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承担肿瘤专科医疗；开展临床教学及研究工作。（涉及资质许可项目须持有效资质证书开展）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广州市横枝岗路78号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李家平</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4896.39万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广州医科大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年05月09日 至 2031年05月08日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2527,7 +2599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -4538,6 +4610,76 @@
         <v>30</v>
       </c>
     </row>
+    <row r="58" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EAA62E4-3CB5-4183-BB91-7595D00E1C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6B114F-39A8-4BA6-B316-CDECD67BA6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="557">
   <si>
     <t>s</t>
   </si>
@@ -2205,6 +2205,42 @@
   </si>
   <si>
     <t>自 2026年05月09日 至 2031年05月08日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>东营市学校体育卫生与艺术教育管理服务中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12370500MB237150XG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FC8D6705C462C0C0EAB515EDDA76C6B1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承担全市中小学体育、卫生与健康教育、艺术教育的管理服务工作；协调指导全市中小学国防教育工作、学生军训工作；组织开展国防教育教研、教改工作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>东营市东城府前街118号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴金生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.55万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>东营市教育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2021年12月27日 至 2027年03月31日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2599,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -4680,6 +4716,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="60" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6B114F-39A8-4BA6-B316-CDECD67BA6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920EE1D3-76D5-4D8B-91BA-3C8DB93CEFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="566">
   <si>
     <t>s</t>
   </si>
@@ -2241,6 +2241,42 @@
   </si>
   <si>
     <t>自 2021年12月27日 至 2027年03月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山东理工大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1237000049557139X7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6BBDB99B2C8EEC6783C72E557D582F5D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面向社会培养高等学历人才，开展教学、科学研究和社会服务等，促进科技文化发展。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淄博市张店区新村西路266号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李玉霞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>202931万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山东省教育厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2022年08月31日 至 2026年03月31日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2635,7 +2671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -4751,6 +4787,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="61" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920EE1D3-76D5-4D8B-91BA-3C8DB93CEFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49442B5D-6054-4F59-A80A-47CCEB5EAD12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="574">
   <si>
     <t>s</t>
   </si>
@@ -2277,6 +2277,38 @@
   </si>
   <si>
     <t>自 2022年08月31日 至 2026年03月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>博山区大数据中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12370304MB28379208</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1457AB8F21CA1ACCCC5B51FF546D7A6E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负责落实国家、省、市政务信息资源共享管理办法、安全保障措施和管理制度；贯彻落实政务信息资源交换、共享、管理和应用的有关政策制度和规范标准；负责协调指导全区电子政务建设和应用、电子政务网络及安全保障工作等。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>博山区县前街46号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王健</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淄博市博山区人民政府办公室（区政府外事办公室、区机关事务管理局、区大数据局）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2022年11月28日 至 2023年03月31日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2671,7 +2703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -4822,6 +4854,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="62" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49442B5D-6054-4F59-A80A-47CCEB5EAD12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57940487-ACD6-45C3-AFFE-9C69FAA08A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="583">
   <si>
     <t>s</t>
   </si>
@@ -2309,6 +2309,42 @@
   </si>
   <si>
     <t>自 2022年11月28日 至 2023年03月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏省人民医院（南京医科大学第一附属医院）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12320000466000838D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8A0B95BEAB8CEEC0511097EBC3CEEABF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为人民身体健康提供医疗与护理保健服务。医疗与护理　医学教学　医学研究　卫生医疗人员进修培训　卫生技术人员继续教育　保健与健康宣传教育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南京市广州路300号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘云</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>差额补贴 （差额补贴）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>133541万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年02月28日 至 2030年02月28日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2703,7 +2739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -4889,6 +4925,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="63" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57940487-ACD6-45C3-AFFE-9C69FAA08A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFB28E8-7E95-495B-8331-9AD70D6348A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="593">
   <si>
     <t>s</t>
   </si>
@@ -2345,6 +2345,46 @@
   </si>
   <si>
     <t>自 2025年02月28日 至 2030年02月28日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新疆大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12650000457601471G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B36FE3EF394676BF4EDB48385D3CC53D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等学历人才，促进科技文化发展。哲学、理学、工学、管理学、法学、文学、历史学等综合类大专、本科、硕士研究生、博士研究生学历教育 博士后培养 相关科学研究、继续教育、专业培训、学术交流等社会服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌鲁木齐市天山区胜利路666号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马新宾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （差额拨款）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>206777万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区人民政府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年09月06日 至 2028年09月05日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2739,7 +2779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -4960,6 +5000,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="64" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFB28E8-7E95-495B-8331-9AD70D6348A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218E6389-39BD-43A5-ADAF-DEC6697CCB1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="622">
   <si>
     <t>s</t>
   </si>
@@ -2385,6 +2385,122 @@
   </si>
   <si>
     <t>自 2023年09月06日 至 2028年09月05日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12330523471280395C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12371700787180796R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12442000MB2D517358</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安吉县文化馆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组织辅导群众业余文艺创作和文化艺术、文艺团队和文化骨干队伍，农村、社区和企业开展业余文艺创作、文化艺术活动娱乐活动，搜集整理民族、民间的文学、艺术遗产；承担文化馆数字化建设。开展全县基层文化和社会宣传教育工作，承办培训、展览、讲座等文化艺术活动。开展公益性群众文化演出、比赛、交流等活动；开展艺术创作，推出艺术精品，开展群众文化理论研究、群文调研和文化交流，开展对外民间文化交流，完善文化档案。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安吉县昌硕街道天目中路573号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛亚伟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政全额补助 （全额拨款）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安吉县文化和广电旅游体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年04月01日 至 2030年04月01日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5EBD9BB7A37FBC6969DA89851392E8A9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9EDBE95C904F3A0A57D7EC2896F9927A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>菏泽市地方戏曲传承研究院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负责山东梆子、枣梆、大弦子戏等地方戏曲的研究、保护、传承和展演工作；承担市级“送戏下乡”等文化惠民演出任务；负责地方戏曲创作和艺术精品打造；负责引进地方戏曲人才和培养后备人才；组织专业人员深入基层，进学校、进社区、进企业，义务辅导、培训基层文艺骨干，活跃城乡群众文化生活；承办党委、政府交办的其他工作任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>菏泽市牡丹南路75号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>徐向东</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>399万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>菏泽市文化和旅游局（市新闻出版广电局、市文物局）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2020年03月18日 至 2025年03月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中山市教育体育旅游发展研究院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>577275930621BF0CCA7BCB9F9694E695</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从事教育、体育、旅游产业发展等领域宣传、理论和应用研究；开展教育、体育、旅游行业及机关企事业单位业务培训与学习交流组织；对托育、学前教育、义务教育和高中以及职业教育等领域开展研究和服务开发；教育、体育、旅游人力资源开发应用；教育、体育、旅游相关产品开发与销售，互联网销售（除销售需要许可的商品）；旅游开发项目策划咨询，研学、休闲农业和乡村旅游资源的开发运营；组织、开展全市性的教育、体育竞赛及相关活动；组织各类活动和赛事；教育培训和咨询；软件技术开发、技术服务、技术咨询；适时发布相关产业年度白皮书及重点调研报告；承接相关部门或单位委托的其他任务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广东省中山市东区中山五路1号中山日报社大楼703室</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赖友生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非财政补助 （经费自理）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>43.82万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中山日报社</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年09月18日 至 2030年09月17日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2779,7 +2895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -5035,6 +5151,111 @@
         <v>30</v>
       </c>
     </row>
+    <row r="65" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218E6389-39BD-43A5-ADAF-DEC6697CCB1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C408CD-2F3B-4146-B800-A5E80910FEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="631">
   <si>
     <t>s</t>
   </si>
@@ -2501,6 +2501,42 @@
   </si>
   <si>
     <t>自 2025年09月18日 至 2030年09月17日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本溪市戏曲艺术剧院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12210500MB0B58886E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAB90A2535C07994F9E0F507CDB4F71B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本溪市平山区工人街道富强街16-1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韦鸿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （财政全部补助、财政部分补助、经费自理）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本溪市文化事业发展服务中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年04月10日 至 2031年04月09日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承担国家、省、市级重大演出任务；承担宣传、公共服务、惠民演出、艺术普及等工作；组织排练、演出、推广京剧、评剧等具有地方特色、民族特色的传统艺术舞台精品剧目；培养戏曲艺术创作、表演人才；加强对基层文艺队伍指导和培训。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2895,7 +2931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -5256,6 +5292,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="68" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C408CD-2F3B-4146-B800-A5E80910FEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E458C0-0E26-43F8-B28E-BB048A314317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="647">
   <si>
     <t>s</t>
   </si>
@@ -2537,6 +2537,70 @@
   </si>
   <si>
     <t>承担国家、省、市级重大演出任务；承担宣传、公共服务、惠民演出、艺术普及等工作；组织排练、演出、推广京剧、评剧等具有地方特色、民族特色的传统艺术舞台精品剧目；培养戏曲艺术创作、表演人才；加强对基层文艺队伍指导和培训。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江西农业大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12360000491015759G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>258C66EA94D0041E6BD253A97F5BEF56</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江西省南昌市志敏大道1101号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄路生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230884万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年05月13日 至 2030年05月12日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等学历农业人才，促进科技、文化、农业发展。植物生产、生物工程、动物生产、农业经济管理、农业工程、计算机工程、食品科学、文学艺术等学科大专、本科、研究生班、硕士研究生、博士研究生学历教育；相关科学研究、继续教育、专业培训、学术交流及相关社会服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山东交通学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12370000495541617L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AA79EC97E30C96ECAB8A796B78FD65AF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面向社会培养交通事业应用型专门人才，进行科学技术研究，开展在职培训、技术咨询、技术服务等社会服务，发挥高校作用，进行文化传承创新和国际交流合作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>济南市交校路5号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孔伟金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>58822万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年12月05日 至 2026年03月31日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2931,7 +2995,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -5327,6 +5391,76 @@
         <v>30</v>
       </c>
     </row>
+    <row r="69" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E458C0-0E26-43F8-B28E-BB048A314317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3DE22F-F7BF-4441-9F58-11C7EBB3CAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="657">
   <si>
     <t>s</t>
   </si>
@@ -2601,6 +2601,46 @@
   </si>
   <si>
     <t>自 2023年12月05日 至 2026年03月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浙江加州国际纳米技术研究院绍兴分院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12330600560990145K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60BCD99B63F79FB29FAF2925EE8DCBA7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产研合作，技术研发与服务，成果转让与推广等（涉及资质许可项目需持有资质证书开展）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绍兴市越城区群贤东路2-1号（群贤大楼）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵凌云</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自收自支 （自收自支）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>117万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绍兴市越城区科学技术局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年03月11日 至 2029年02月05日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2995,7 +3035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -5461,6 +5501,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="71" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3DE22F-F7BF-4441-9F58-11C7EBB3CAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6DB30B1-F852-43AC-B6BB-F9D8CCA8EA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="666">
   <si>
     <t>s</t>
   </si>
@@ -2641,6 +2641,42 @@
   </si>
   <si>
     <t>自 2026年03月11日 至 2029年02月05日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石家庄铁路职业技术学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12130000401706362A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5925295BD90CFD66373DAF341B18DFF3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等专科学历应用人才，促进科技发展。铁道工程、建筑、测绘、信息工程、电气工程、轨道交通（机电工程）、会计、营销、物流、会展、旅游、酒店、文秘、乘务等高等专科学历教育，相关科学研究和技术服务，继续教育，专业培训，学术交流。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石家庄市四水厂路18号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李素英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16394.32万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河北省教育厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年10月15日 至 2030年10月14日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3035,7 +3071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -5536,6 +5572,76 @@
         <v>30</v>
       </c>
     </row>
+    <row r="72" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6DB30B1-F852-43AC-B6BB-F9D8CCA8EA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F29C1D1-BE09-4022-9EC5-2C6777A414F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="674">
   <si>
     <t>s</t>
   </si>
@@ -2677,6 +2677,38 @@
   </si>
   <si>
     <t>自 2025年10月15日 至 2030年10月14日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滁州学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123400004860905355</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E498417EA4DC2AD514DD70FFE74FF1BD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养本科层次高等学历人才，促进教育事业发展,为地方经济社会发展服务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安徽省滁州市琅琊西路2号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>周旭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23879万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年06月03日 至 2031年06月02日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3071,7 +3103,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -5642,6 +5674,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="74" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F29C1D1-BE09-4022-9EC5-2C6777A414F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEEDF74C-5D7D-4E53-ABFD-EA787D8A319E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="683">
   <si>
     <t>s</t>
   </si>
@@ -2709,6 +2709,42 @@
   </si>
   <si>
     <t>自 2026年06月03日 至 2031年06月02日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123709004941925582</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D8F2BA5999C882792BB4F218FF3997F4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰山职业技术学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养工业、农业、经管类高等技术应用型人才，进行高职教育教学研究，为经济社会发展服务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰安市天烛峰路281号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崔耕虎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>33273.43万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰安市人民政府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年02月22日 至 2026年03月31日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3103,7 +3139,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -5709,6 +5745,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="75" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7C59F2-D407-47AD-928B-B1874013CCF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A112C65-ADEF-4354-BC65-D9CC98EBE9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="131">
   <si>
     <t>s</t>
   </si>
@@ -498,6 +498,46 @@
   </si>
   <si>
     <t>1123212</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宣汉县体育发展服务中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12511422008822869Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9FDB0FFDC599C0D7053E560AE751247D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>推行全民健身计划；组织体育赛事活动；实施国家体育锻炼标准，开展国民体质监测；负责体育产业发展服务工作；实施“全民健身路径工程”和“农民体育健身工程”；对体育彩票进行协管。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宣汉县东乡街道育才社区多宝寺路277号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贾志杰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宣汉县人民政府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年06月08日 至 2029年06月07日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -892,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1363,6 +1403,41 @@
         <v>20</v>
       </c>
     </row>
+    <row r="14" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A112C65-ADEF-4354-BC65-D9CC98EBE9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906E105B-E8FF-4DF3-8110-39B30CC770C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="139">
   <si>
     <t>s</t>
   </si>
@@ -538,6 +538,38 @@
   </si>
   <si>
     <t>自 2026年06月08日 至 2029年06月07日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安庆师范大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123400004856178921</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2A25635317077AF0683D935CB474AE50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高等学历教育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安庆市菱湖南路128号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>彭凤莲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11451万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年03月31日 至 2028年03月31日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -932,7 +964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1438,6 +1470,41 @@
         <v>20</v>
       </c>
     </row>
+    <row r="15" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906E105B-E8FF-4DF3-8110-39B30CC770C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AFC028-67FF-41E4-B705-7E510A461B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="148">
   <si>
     <t>s</t>
   </si>
@@ -570,6 +570,42 @@
   </si>
   <si>
     <t>自 2023年03月31日 至 2028年03月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷山县苗族银饰刺绣博物馆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12522634584144672J</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0B5330E5C462E557F4B3D1D3A7CC035F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宣传苗族文明成就的重要窗口 承担苗族服饰文化的研究和传播苗族文化。制定博物馆相关的章程、掌握服饰文化与相关文博发展趋势、提出工作设想、拟定博物馆建设和发展规划 负责馆内苗族服饰文化资料的编辑、文物的归档及文物的展示、馆内文物的管理 维护 修复 安全和日常卫生保洁等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷山县丹江镇银饰刺绣创意中心一条街</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>彭祖德</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>95.5万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷山县文体广电旅游局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年02月15日 至 2028年02月15日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -964,7 +1000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1505,6 +1541,41 @@
         <v>20</v>
       </c>
     </row>
+    <row r="16" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AFC028-67FF-41E4-B705-7E510A461B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0721B1EA-6C0C-4360-A131-14F09B09D65E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="117">
   <si>
     <t>s</t>
   </si>
@@ -149,18 +149,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>安徽省教育厅</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>财政拨款</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>财政补助 （全额拨款）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -177,118 +169,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>12371700787180796R</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12442000MB2D517358</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9EDBE95C904F3A0A57D7EC2896F9927A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>菏泽市地方戏曲传承研究院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>负责山东梆子、枣梆、大弦子戏等地方戏曲的研究、保护、传承和展演工作；承担市级“送戏下乡”等文化惠民演出任务；负责地方戏曲创作和艺术精品打造；负责引进地方戏曲人才和培养后备人才；组织专业人员深入基层，进学校、进社区、进企业，义务辅导、培训基层文艺骨干，活跃城乡群众文化生活；承办党委、政府交办的其他工作任务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>菏泽市牡丹南路75号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>徐向东</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>399万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>菏泽市文化和旅游局（市新闻出版广电局、市文物局）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2020年03月18日 至 2025年03月31日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中山市教育体育旅游发展研究院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>577275930621BF0CCA7BCB9F9694E695</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从事教育、体育、旅游产业发展等领域宣传、理论和应用研究；开展教育、体育、旅游行业及机关企事业单位业务培训与学习交流组织；对托育、学前教育、义务教育和高中以及职业教育等领域开展研究和服务开发；教育、体育、旅游人力资源开发应用；教育、体育、旅游相关产品开发与销售，互联网销售（除销售需要许可的商品）；旅游开发项目策划咨询，研学、休闲农业和乡村旅游资源的开发运营；组织、开展全市性的教育、体育竞赛及相关活动；组织各类活动和赛事；教育培训和咨询；软件技术开发、技术服务、技术咨询；适时发布相关产业年度白皮书及重点调研报告；承接相关部门或单位委托的其他任务。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广东省中山市东区中山五路1号中山日报社大楼703室</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赖友生</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>非财政补助 （经费自理）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>43.82万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中山日报社</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2025年09月18日 至 2030年09月17日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本溪市戏曲艺术剧院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12210500MB0B58886E</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CAB90A2535C07994F9E0F507CDB4F71B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本溪市平山区工人街道富强街16-1号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>韦鸿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助 （财政全部补助、财政部分补助、经费自理）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本溪市文化事业发展服务中心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2026年04月10日 至 2031年04月09日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>承担国家、省、市级重大演出任务；承担宣传、公共服务、惠民演出、艺术普及等工作；组织排练、演出、推广京剧、评剧等具有地方特色、民族特色的传统艺术舞台精品剧目；培养戏曲艺术创作、表演人才；加强对基层文艺队伍指导和培训。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>江西农业大学</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -353,46 +233,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>浙江加州国际纳米技术研究院绍兴分院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12330600560990145K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>60BCD99B63F79FB29FAF2925EE8DCBA7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产研合作，技术研发与服务，成果转让与推广等（涉及资质许可项目需持有资质证书开展）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>绍兴市越城区群贤东路2-1号（群贤大楼）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赵凌云</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自收自支 （自收自支）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>117万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>绍兴市越城区科学技术局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2026年03月11日 至 2029年02月05日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>石家庄铁路职业技术学院</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -606,6 +446,42 @@
   </si>
   <si>
     <t>自 2023年02月15日 至 2028年02月15日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>六枝特区生态博物馆（中国贵州六枝梭戛生态博物馆）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1180FCD05770DD1504848663E5B32AF0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12520203429361271L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挖掘保护民族文化， 推进民族文化发展。保护以长角为头饰的苗族文化遗产与自然遗产 收集整理箐苗的记忆、文字、图片、录音、录像等资料 对箐苗文化进行研究并推出成果 强化箐苗文化的宣传推广、利用箐苗研究发展成果助推箐苗社区经济发展 承办主管部门交办的其他工作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>六枝特区梭戛乡高兴村陇嘎寨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余瑜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>39.53万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>六枝特区文体广电旅游局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年02月12日 至 2031年02月12日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1000,7 +876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1053,7 +929,7 @@
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -1088,34 +964,34 @@
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="G3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="I3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>20</v>
@@ -1123,34 +999,34 @@
     </row>
     <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="G4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="I4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>20</v>
@@ -1158,34 +1034,34 @@
     </row>
     <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="J5" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>20</v>
@@ -1193,34 +1069,34 @@
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="G6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>20</v>
@@ -1228,34 +1104,34 @@
     </row>
     <row r="7" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>20</v>
@@ -1263,34 +1139,34 @@
     </row>
     <row r="8" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>20</v>
@@ -1298,34 +1174,34 @@
     </row>
     <row r="9" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>20</v>
@@ -1333,34 +1209,34 @@
     </row>
     <row r="10" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>20</v>
@@ -1368,34 +1244,34 @@
     </row>
     <row r="11" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>20</v>
@@ -1403,34 +1279,34 @@
     </row>
     <row r="12" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>20</v>
@@ -1438,141 +1314,36 @@
     </row>
     <row r="13" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="K16" s="1" t="s">
         <v>20</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0721B1EA-6C0C-4360-A131-14F09B09D65E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0389CAF7-36FC-417D-9F09-FB0CB9AC44AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="118">
   <si>
     <t>s</t>
   </si>
@@ -482,6 +482,10 @@
   </si>
   <si>
     <t>自 2026年02月12日 至 2031年02月12日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23F5B2D592C845DFD1A67627C7804C17</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -876,7 +880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1347,6 +1351,41 @@
         <v>20</v>
       </c>
     </row>
+    <row r="14" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0389CAF7-36FC-417D-9F09-FB0CB9AC44AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC2E9BB-94C1-4223-B4A2-A1F3DFCEAB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="128">
   <si>
     <t>s</t>
   </si>
@@ -486,6 +486,46 @@
   </si>
   <si>
     <t>23F5B2D592C845DFD1A67627C7804C17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CEC8CB310D7D3D58E41EA4C5A44C7BA4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邢台市信都区电视台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12130521772769637R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电视节目制作、播出、转播；电视产业经营；电视研究。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邢台市中兴西路292号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李敏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （差额补贴）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>536万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邢台市信都区融媒体中心（邢台市信都区广播电视台）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2022年03月03日 至 2027年03月03日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -880,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1386,6 +1426,41 @@
         <v>20</v>
       </c>
     </row>
+    <row r="15" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC2E9BB-94C1-4223-B4A2-A1F3DFCEAB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE4F872-AB8D-421F-BE2F-6E28736E8211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="120">
   <si>
     <t>s</t>
   </si>
@@ -109,42 +109,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>阳泉市体育产业发展中心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12140300MB169311X6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A65360433A2D87BF49C097293D1F5DB4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>张超</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.8万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阳泉市城区南大街452号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>推动全市体育产业发展。制定全市体育产业发展规划 推进全市体育产业发展 监测分析全市体育产业运行态势 协调解决体育产业发展过程中的重大问题 规范和培育体育产业市场 监督、检查和管理全市体育经营活动 协助开展城、矿区体育市场执法检查工作 保护合法经营 制止和查处违法行为 开展对体育产业从业人员的培训 参与体育产业经营场所标准的验收评估</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阳泉市体育局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2023年06月06日 至 2028年06月05日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>全额拨款</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -341,46 +305,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>宣汉县体育发展服务中心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12511422008822869Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9FDB0FFDC599C0D7053E560AE751247D</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>推行全民健身计划；组织体育赛事活动；实施国家体育锻炼标准，开展国民体质监测；负责体育产业发展服务工作；实施“全民健身路径工程”和“农民体育健身工程”；对体育彩票进行协管。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宣汉县东乡街道育才社区多宝寺路277号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>贾志杰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>财政补助</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宣汉县人民政府</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2026年06月08日 至 2029年06月07日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>安庆师范大学</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -526,6 +454,46 @@
   </si>
   <si>
     <t>自 2022年03月03日 至 2027年03月03日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12232736414650302A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09DC4C2460EF71D0D4F9E51073FF6CCF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新林广播电视台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广播新闻和其它信息，促进社会经济文化发展。 新闻广播 专题广播 文艺广播</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新林镇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许会波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非财政补助 （经费自理）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>436万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新林区政府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年11月19日 至 2029年11月18日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -920,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -973,7 +941,7 @@
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -1008,34 +976,34 @@
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>43</v>
-      </c>
       <c r="I3" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>20</v>
@@ -1043,34 +1011,34 @@
     </row>
     <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>20</v>
@@ -1078,34 +1046,34 @@
     </row>
     <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>20</v>
@@ -1113,34 +1081,34 @@
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>43</v>
-      </c>
       <c r="I6" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>20</v>
@@ -1148,34 +1116,34 @@
     </row>
     <row r="7" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>20</v>
@@ -1183,34 +1151,34 @@
     </row>
     <row r="8" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>20</v>
@@ -1218,34 +1186,34 @@
     </row>
     <row r="9" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>30</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>20</v>
@@ -1271,16 +1239,16 @@
         <v>86</v>
       </c>
       <c r="G10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="I10" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="J10" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>20</v>
@@ -1288,31 +1256,31 @@
     </row>
     <row r="11" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>92</v>
       </c>
       <c r="D11" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="I11" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>98</v>
@@ -1323,34 +1291,34 @@
     </row>
     <row r="12" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>20</v>
@@ -1358,34 +1326,34 @@
     </row>
     <row r="13" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>20</v>
@@ -1393,71 +1361,36 @@
     </row>
     <row r="14" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="I14" s="5" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="K15" s="1" t="s">
         <v>20</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE4F872-AB8D-421F-BE2F-6E28736E8211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0599DC-EE79-4792-8525-1789C21599CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="137">
   <si>
     <t>s</t>
   </si>
@@ -494,6 +494,74 @@
   </si>
   <si>
     <t>自 2024年11月19日 至 2029年11月18日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>六盘水职业技术学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>125202007501646610</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等专科学历技术应用人才，促进科技文化发展。 培养高等专科、中专学历教育 开展成人学历教育和各种职业技术培训 培养适用性复合型人才 建设学生实习、实训基地 承担有关科研项目 开展学术交流活动及相关社会服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>六盘水市钟山区钟山大道西段1119号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贺明卫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35311.17万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>六盘水市人民政府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年01月04日 至 2031年01月04日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安徽科技工程大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12340000486166325F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等学历师资人才，促进教育事业发展。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安徽省滁州市凤阳县东华路</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李升和</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101075万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年11月28日 至 2029年11月27日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CB5301EC21231BEC9A800BED0455BE25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E42AAAC40AB62E612AD5DBDB0ACA06C8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -888,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1394,6 +1462,76 @@
         <v>20</v>
       </c>
     </row>
+    <row r="15" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0599DC-EE79-4792-8525-1789C21599CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DC1B3D-6292-440E-8093-BB91F6CE431E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="147">
   <si>
     <t>s</t>
   </si>
@@ -562,6 +562,46 @@
   </si>
   <si>
     <t>E42AAAC40AB62E612AD5DBDB0ACA06C8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8619583C559B70E654BA842D3CDEF9E8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12330000470009026T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杭州电子科技大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高学历人才，促进科技文化发展。研究生、本专科、成人、高职教育和相应的科学研究、技术开发、科技产业（涉及资质许可项目需持有资质证书开展）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浙江省杭州市下沙高教园区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任奎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政适当补助 （财政适当补助）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>201927.92万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浙江省人民政府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年08月10日 至 2027年03月14日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -956,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1532,6 +1572,41 @@
         <v>20</v>
       </c>
     </row>
+    <row r="17" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DC1B3D-6292-440E-8093-BB91F6CE431E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5F730F-4F0D-4854-8EDA-32A5C498D4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="157">
   <si>
     <t>s</t>
   </si>
@@ -602,6 +602,46 @@
   </si>
   <si>
     <t>自 2026年08月10日 至 2027年03月14日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0E19F770E6ED7C59171C0854DCB44C28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新昌县教育发展中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12330624MB1L55037K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参与全县教育改革发展重大问题的调查和研究、全县教育事业发展中长期规划的拟订、各类学校综合性创建的技术指导和行政辅助工作。区域教育合作具体事务 学校综合性创建指导 学校党建工作指导 全县教育改革发展重大问题调查和研究 全县教育事业发展中长期规划拟订</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浙江省新昌县七星街道桃源路35号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石英俊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政全额补助</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新昌县教育体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年12月14日 至 2027年09月06日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -996,7 +1036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1607,6 +1647,41 @@
         <v>20</v>
       </c>
     </row>
+    <row r="18" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5F730F-4F0D-4854-8EDA-32A5C498D4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3548B64B-5C4C-494E-9853-12A5669A235C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="196">
   <si>
     <t>s</t>
   </si>
@@ -642,6 +642,162 @@
   </si>
   <si>
     <t>自 2023年12月14日 至 2027年09月06日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广东梅州职业技术学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新疆大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白银矿冶职业技术学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C72E218F9E5FFD4ED6FFCDF8AF2408A7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏省连云港中等专业学校（连云港市旅游学校、连云港市高级技工学校）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12320700468052383C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贯彻落实国家中等职业教育方针和民族政策，开展中等职业教育培训，实施素质教育，培养高技能人才；落实民族班办学方针、政策，促进职业教育发展和民族团结。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏省连云港市海州区云台山风景区振华路2号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李大勇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>差额补贴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16536万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连云港市教育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年12月20日 至 2028年12月20日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12441400MB2D828492</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>06C641FBD834F230C18534E1FC6A2D9C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承担普通高、中等职业教育和成人学历教育；承担各类继续教育、职业技能培训和鉴定；开展科学研究和社会服务工作；开展国内外、校际教育合作与学术交流。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅州市梅江区学院路15号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>董芳远</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （财政核补）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25000万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅州市人民政府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年07月29日 至 2031年07月28日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12650000457601471G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B36FE3EF394676BF4EDB48385D3CC53D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等学历人才，促进科技文化发展。哲学、理学、工学、管理学、法学、文学、历史学等综合类大专、本科、硕士研究生、博士研究生学历教育 博士后培养 相关科学研究、继续教育、专业培训、学术交流等社会服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌鲁木齐市天山区胜利路666号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马新宾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （差额拨款）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>206777万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区人民政府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年09月06日 至 2028年09月05日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12620400665441476E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4B09D47326216AFEA6F9A93E12014A58</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以就业为导向，服务地方经济为目标，培养合格的高等职业技术人才。实施普通高等职业教育和技工教育，开展成人高等教育，积极拓展社会培训和服务功能。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白银市白银区南环路1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>师永波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70175万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白银市教育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2022年04月22日 至 2027年04月22日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1036,7 +1192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1682,6 +1838,146 @@
         <v>20</v>
       </c>
     </row>
+    <row r="19" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3548B64B-5C4C-494E-9853-12A5669A235C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BDB4A7-88FF-4062-9E73-35E57E17ABDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,38 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="145">
   <si>
     <t>s</t>
   </si>
   <si>
-    <t>测试内容1</t>
-  </si>
-  <si>
-    <t>测试内容2</t>
-  </si>
-  <si>
-    <t>测试内容3</t>
-  </si>
-  <si>
-    <t>测试内容4</t>
-  </si>
-  <si>
-    <t>测试内容5</t>
-  </si>
-  <si>
-    <t>测试内容6</t>
-  </si>
-  <si>
-    <t>测试内容7</t>
-  </si>
-  <si>
-    <t>测试内容8</t>
-  </si>
-  <si>
-    <t>测试内容10</t>
-  </si>
-  <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -105,10 +78,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>自 2000年00月00日 至 2000年00月00日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>全额拨款</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -301,10 +270,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1123212</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>财政补助</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -341,162 +306,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>雷山县苗族银饰刺绣博物馆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12522634584144672J</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0B5330E5C462E557F4B3D1D3A7CC035F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宣传苗族文明成就的重要窗口 承担苗族服饰文化的研究和传播苗族文化。制定博物馆相关的章程、掌握服饰文化与相关文博发展趋势、提出工作设想、拟定博物馆建设和发展规划 负责馆内苗族服饰文化资料的编辑、文物的归档及文物的展示、馆内文物的管理 维护 修复 安全和日常卫生保洁等</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷山县丹江镇银饰刺绣创意中心一条街</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>彭祖德</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>95.5万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷山县文体广电旅游局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2023年02月15日 至 2028年02月15日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>六枝特区生态博物馆（中国贵州六枝梭戛生态博物馆）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1180FCD05770DD1504848663E5B32AF0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12520203429361271L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>挖掘保护民族文化， 推进民族文化发展。保护以长角为头饰的苗族文化遗产与自然遗产 收集整理箐苗的记忆、文字、图片、录音、录像等资料 对箐苗文化进行研究并推出成果 强化箐苗文化的宣传推广、利用箐苗研究发展成果助推箐苗社区经济发展 承办主管部门交办的其他工作。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>六枝特区梭戛乡高兴村陇嘎寨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余瑜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>39.53万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>六枝特区文体广电旅游局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2026年02月12日 至 2031年02月12日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>23F5B2D592C845DFD1A67627C7804C17</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CEC8CB310D7D3D58E41EA4C5A44C7BA4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>邢台市信都区电视台</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12130521772769637R</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>电视节目制作、播出、转播；电视产业经营；电视研究。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>邢台市中兴西路292号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李敏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助 （差额补贴）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>536万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>邢台市信都区融媒体中心（邢台市信都区广播电视台）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2022年03月03日 至 2027年03月03日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12232736414650302A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>09DC4C2460EF71D0D4F9E51073FF6CCF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新林广播电视台</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广播新闻和其它信息，促进社会经济文化发展。 新闻广播 专题广播 文艺广播</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新林镇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>许会波</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>非财政补助 （经费自理）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>436万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新林区政府</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2024年11月19日 至 2029年11月18日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>六盘水职业技术学院</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -605,46 +418,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0E19F770E6ED7C59171C0854DCB44C28</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新昌县教育发展中心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12330624MB1L55037K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>参与全县教育改革发展重大问题的调查和研究、全县教育事业发展中长期规划的拟订、各类学校综合性创建的技术指导和行政辅助工作。区域教育合作具体事务 学校综合性创建指导 学校党建工作指导 全县教育改革发展重大问题调查和研究 全县教育事业发展中长期规划拟订</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>浙江省新昌县七星街道桃源路35号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>石英俊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政全额补助</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>300万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新昌县教育体育局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2023年12月14日 至 2027年09月06日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>广东梅州职业技术学院</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -798,6 +571,38 @@
   </si>
   <si>
     <t>自 2022年04月22日 至 2027年04月22日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河北工业大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>121300004017050446</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4BF5CF264AC2535E437DDE72D57D360B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高等教育及科学研究。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天津市北辰区双口镇西平道5340号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王利民</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>247493万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年12月31日 至 2029年12月30日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -836,7 +641,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -852,12 +657,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -895,7 +694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -907,9 +706,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1192,18 +988,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
-    <col min="2" max="2" width="27.3984375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="18.9296875" style="5"/>
-    <col min="4" max="4" width="21" style="5" customWidth="1"/>
-    <col min="5" max="5" width="30.59765625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="12.59765625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="14" style="5" customWidth="1"/>
-    <col min="8" max="8" width="14.265625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="18.9296875" style="5"/>
+    <col min="2" max="2" width="27.3984375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.9296875" style="4"/>
+    <col min="4" max="4" width="21" style="4" customWidth="1"/>
+    <col min="5" max="5" width="30.59765625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="12.59765625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14" style="4" customWidth="1"/>
+    <col min="8" max="8" width="14.265625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="18.9296875" style="4"/>
     <col min="10" max="10" width="18.9296875" style="3"/>
     <col min="11" max="16384" width="18.9296875" style="1"/>
   </cols>
@@ -1213,769 +1009,594 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="F2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="K2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="G4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="J4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>52</v>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>27</v>
+        <v>46</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="G7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="J7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="G8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="K8" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>24</v>
+        <v>70</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="B10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>88</v>
+      <c r="D10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>69</v>
+        <v>88</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B13" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="F13" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="G13" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>108</v>
       </c>
+      <c r="I13" s="4" t="s">
+        <v>109</v>
+      </c>
       <c r="J13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="4" t="s">
         <v>118</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>119</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B15" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H15" s="5" t="s">
+      <c r="G15" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="H15" s="4" t="s">
         <v>126</v>
       </c>
+      <c r="I15" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="J15" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="K16" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="I17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BDB4A7-88FF-4062-9E73-35E57E17ABDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACB9E91-DCA2-4DB3-91B0-993049E5F9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="154">
   <si>
     <t>s</t>
   </si>
@@ -603,6 +603,42 @@
   </si>
   <si>
     <t>自 2024年12月31日 至 2029年12月30日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ABA98B9BC286D6957C4A29991736A24A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苏州杂志社</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12320500466954885X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弘扬吴文化，服务精神文明建设。 出版《苏州杂志》双月期刊。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苏州市滚绣坊青石弄5号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朱红梅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38.83万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苏州市文学艺术界联合会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年02月24日 至 2030年02月24日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -988,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1599,6 +1635,41 @@
         <v>11</v>
       </c>
     </row>
+    <row r="18" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACB9E91-DCA2-4DB3-91B0-993049E5F9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FB405B-0A1B-4843-8F6E-09C8BF8CF109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="163">
   <si>
     <t>s</t>
   </si>
@@ -639,6 +639,42 @@
   </si>
   <si>
     <t>自 2025年02月24日 至 2030年02月24日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B608A612038807B0181B1B4C50A2D9F2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广西科技大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>124500004985963814</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等学历人才，开展硕士研究生和本专科学历教育，并进行相关科学研究、继续教育、专业培训、学术交流和相关社会服务，以促进科技发展和社会进步。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柳州市文昌路2号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘宝臣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>94505.9万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广西壮族自治区教育厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年03月18日 至 2030年03月17日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1024,7 +1060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1670,6 +1706,41 @@
         <v>11</v>
       </c>
     </row>
+    <row r="19" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FB405B-0A1B-4843-8F6E-09C8BF8CF109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAAF1EF-DCAD-46F8-8F20-222499E015E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="172">
   <si>
     <t>s</t>
   </si>
@@ -675,6 +675,42 @@
   </si>
   <si>
     <t>自 2025年03月18日 至 2030年03月17日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>121500004600222007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>88446CF827EA575A10369E0A80DBF808</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古电子信息职业技术学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坚持把铸牢中华民族共同体意识作为教育工作的主线 贯穿于办学治校 教书育人 科学研究 人才培养 服务社会等全过程各方面 培养大专学历和本科学历人才 从事电子信息学科 高等职业教育 大专教育 本科教育 中专教育和学科继续教育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古呼和浩特市赛罕区苏尔干街8号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林民</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>103517万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古自治区教育厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2022年03月24日 至 2027年03月24日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1060,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1741,6 +1777,41 @@
         <v>11</v>
       </c>
     </row>
+    <row r="20" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAAF1EF-DCAD-46F8-8F20-222499E015E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97610A48-43EA-4B7A-B2E9-C8BFFAA9AE22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="154">
   <si>
     <t>s</t>
   </si>
@@ -86,122 +86,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>财政补助 （全额拨款）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>财政补助 （财政拨款）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>江西省人民政府</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>山东省教育厅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>江西农业大学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12360000491015759G</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>258C66EA94D0041E6BD253A97F5BEF56</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>江西省南昌市志敏大道1101号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄路生</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>230884万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2025年05月13日 至 2030年05月12日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>培养高等学历农业人才，促进科技、文化、农业发展。植物生产、生物工程、动物生产、农业经济管理、农业工程、计算机工程、食品科学、文学艺术等学科大专、本科、研究生班、硕士研究生、博士研究生学历教育；相关科学研究、继续教育、专业培训、学术交流及相关社会服务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>山东交通学院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12370000495541617L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AA79EC97E30C96ECAB8A796B78FD65AF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>面向社会培养交通事业应用型专门人才，进行科学技术研究，开展在职培训、技术咨询、技术服务等社会服务，发挥高校作用，进行文化传承创新和国际交流合作。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>济南市交校路5号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>孔伟金</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>58822万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2023年12月05日 至 2026年03月31日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>石家庄铁路职业技术学院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12130000401706362A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5925295BD90CFD66373DAF341B18DFF3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>培养高等专科学历应用人才，促进科技发展。铁道工程、建筑、测绘、信息工程、电气工程、轨道交通（机电工程）、会计、营销、物流、会展、旅游、酒店、文秘、乘务等高等专科学历教育，相关科学研究和技术服务，继续教育，专业培训，学术交流。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>石家庄市四水厂路18号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李素英</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16394.32万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>河北省教育厅</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>自 2025年10月15日 至 2030年10月14日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>滁州学院</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -711,6 +603,42 @@
   </si>
   <si>
     <t>自 2022年03月24日 至 2027年03月24日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0CC57AED37C296D822B0DA1F4760B044</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连云港市体育训练中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12320700MB0598663C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>促进田径，皮、划、赛艇，自行车，拳击运动发展。后备人才培养与输送。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏省连云港市科教创业园区霞晖路99号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>徐庚勇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>141万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连云港市体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年12月10日 至 2029年12月10日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1096,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1149,34 +1077,34 @@
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>11</v>
@@ -1184,34 +1112,34 @@
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="G3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>11</v>
@@ -1237,16 +1165,16 @@
         <v>40</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>11</v>
@@ -1254,34 +1182,34 @@
     </row>
     <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>11</v>
@@ -1289,7 +1217,7 @@
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>44</v>
@@ -1298,22 +1226,22 @@
         <v>45</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>51</v>
@@ -1324,34 +1252,34 @@
     </row>
     <row r="7" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="4" t="s">
+      <c r="I7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>11</v>
@@ -1359,34 +1287,34 @@
     </row>
     <row r="8" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>68</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>11</v>
@@ -1394,34 +1322,34 @@
     </row>
     <row r="9" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>11</v>
@@ -1429,34 +1357,34 @@
     </row>
     <row r="10" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>11</v>
@@ -1464,34 +1392,34 @@
     </row>
     <row r="11" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>11</v>
@@ -1499,34 +1427,34 @@
     </row>
     <row r="12" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -1534,34 +1462,34 @@
     </row>
     <row r="13" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>11</v>
@@ -1569,34 +1497,34 @@
     </row>
     <row r="14" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>116</v>
+        <v>13</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>11</v>
@@ -1604,34 +1532,34 @@
     </row>
     <row r="15" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>125</v>
+        <v>34</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>11</v>
@@ -1639,34 +1567,34 @@
     </row>
     <row r="16" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>11</v>
@@ -1674,141 +1602,36 @@
     </row>
     <row r="17" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>42</v>
+        <v>152</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K20" s="1" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97610A48-43EA-4B7A-B2E9-C8BFFAA9AE22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E37C64-D5E8-4D89-B7ED-98D01DC0E411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="146">
   <si>
     <t>s</t>
   </si>
@@ -94,46 +94,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>滁州学院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>123400004860905355</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E498417EA4DC2AD514DD70FFE74FF1BD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>培养本科层次高等学历人才，促进教育事业发展,为地方经济社会发展服务。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安徽省滁州市琅琊西路2号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>周旭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>23879万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2026年06月03日 至 2031年06月02日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>123709004941925582</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>D8F2BA5999C882792BB4F218FF3997F4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>泰山职业技术学院</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -166,38 +130,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>安庆师范大学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>123400004856178921</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2A25635317077AF0683D935CB474AE50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高等学历教育</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安庆市菱湖南路128号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>彭凤莲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11451万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2023年03月31日 至 2028年03月31日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>23F5B2D592C845DFD1A67627C7804C17</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -639,6 +571,42 @@
   </si>
   <si>
     <t>自 2024年12月10日 至 2029年12月10日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E07B841B0DF4BBB01F601E595A5FC840</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古机电职业技术学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12150000460027503M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坚持把铸牢中华民族共同体意识作为教育工作的主线 贯穿于办学治校 教书育人 科学研究 人才培养 服务社会等全过程各方面 面向行业 服务全区 以高等职业教育为主体 兼办中等职业教育和成人继续教育，开展科学研究、技术服务、培训、技术转移及成果转化等业务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>呼和浩特市赛罕区学府路1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵卫国</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （全额拨款）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40226万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年03月23日 至 2028年03月23日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1024,7 +992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1077,31 +1045,31 @@
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>24</v>
@@ -1112,34 +1080,34 @@
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="H3" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>11</v>
@@ -1147,7 +1115,7 @@
     </row>
     <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>35</v>
@@ -1156,25 +1124,25 @@
         <v>36</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>11</v>
@@ -1182,34 +1150,34 @@
     </row>
     <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>11</v>
@@ -1217,34 +1185,34 @@
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="D6" s="4" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>11</v>
@@ -1252,34 +1220,34 @@
     </row>
     <row r="7" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>11</v>
@@ -1287,34 +1255,34 @@
     </row>
     <row r="8" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>11</v>
@@ -1322,34 +1290,34 @@
     </row>
     <row r="9" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>11</v>
@@ -1357,34 +1325,34 @@
     </row>
     <row r="10" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>11</v>
@@ -1392,34 +1360,34 @@
     </row>
     <row r="11" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>11</v>
@@ -1427,34 +1395,34 @@
     </row>
     <row r="12" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -1462,34 +1430,34 @@
     </row>
     <row r="13" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>16</v>
+        <v>126</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>11</v>
@@ -1497,34 +1465,34 @@
     </row>
     <row r="14" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>11</v>
@@ -1532,106 +1500,36 @@
     </row>
     <row r="15" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K17" s="1" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E37C64-D5E8-4D89-B7ED-98D01DC0E411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DBB4E3-A60F-4B7A-9FE4-15669E44C6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="127">
   <si>
     <t>s</t>
   </si>
@@ -74,18 +74,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>财政补贴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>全额拨款</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>安徽省教育厅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>财政补助 （财政拨款）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -94,114 +86,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>123709004941925582</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>泰山职业技术学院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>培养工业、农业、经管类高等技术应用型人才，进行高职教育教学研究，为经济社会发展服务。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>泰安市天烛峰路281号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>崔耕虎</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>33273.43万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>泰安市人民政府</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2023年02月22日 至 2026年03月31日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>财政补助</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>23F5B2D592C845DFD1A67627C7804C17</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>六盘水职业技术学院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>125202007501646610</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>培养高等专科学历技术应用人才，促进科技文化发展。 培养高等专科、中专学历教育 开展成人学历教育和各种职业技术培训 培养适用性复合型人才 建设学生实习、实训基地 承担有关科研项目 开展学术交流活动及相关社会服务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>六盘水市钟山区钟山大道西段1119号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>贺明卫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>35311.17万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>六盘水市人民政府</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2026年01月04日 至 2031年01月04日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安徽科技工程大学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12340000486166325F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>培养高等学历师资人才，促进教育事业发展。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安徽省滁州市凤阳县东华路</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李升和</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>101075万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2024年11月28日 至 2029年11月27日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CB5301EC21231BEC9A800BED0455BE25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E42AAAC40AB62E612AD5DBDB0ACA06C8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>8619583C559B70E654BA842D3CDEF9E8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -607,6 +495,42 @@
   </si>
   <si>
     <t>自 2023年03月23日 至 2028年03月23日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天长市社会福利院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12341181F14339784T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0189DF92EDC0B0177A49C44938D21167</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供收养服务，弘扬救助精神。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天长市冶山镇塔山村</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴万兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.55万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天长市民政局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年02月21日 至 2030年02月20日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -992,7 +916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1045,7 +969,7 @@
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>18</v>
@@ -1063,16 +987,16 @@
         <v>21</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>11</v>
@@ -1080,34 +1004,34 @@
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>11</v>
@@ -1115,34 +1039,34 @@
     </row>
     <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>11</v>
@@ -1150,34 +1074,34 @@
     </row>
     <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>11</v>
@@ -1185,34 +1109,34 @@
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>11</v>
@@ -1220,34 +1144,34 @@
     </row>
     <row r="7" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="I7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>11</v>
@@ -1255,34 +1179,34 @@
     </row>
     <row r="8" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="G8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>11</v>
@@ -1290,34 +1214,34 @@
     </row>
     <row r="9" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="G9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>11</v>
@@ -1325,34 +1249,34 @@
     </row>
     <row r="10" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="G10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="I10" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>11</v>
@@ -1360,34 +1284,34 @@
     </row>
     <row r="11" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="I11" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="J11" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>11</v>
@@ -1395,34 +1319,34 @@
     </row>
     <row r="12" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>116</v>
       </c>
       <c r="I12" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -1433,103 +1357,33 @@
         <v>120</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>119</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="4" t="s">
+      <c r="I13" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="J13" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="K13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="K15" s="1" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DBB4E3-A60F-4B7A-9FE4-15669E44C6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0250AE8-BDE8-4DB3-8393-85F3CEB5C17A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="89">
   <si>
     <t>s</t>
   </si>
@@ -82,242 +82,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>河北省教育厅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>财政补助</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>8619583C559B70E654BA842D3CDEF9E8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12330000470009026T</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>杭州电子科技大学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>培养高学历人才，促进科技文化发展。研究生、本专科、成人、高职教育和相应的科学研究、技术开发、科技产业（涉及资质许可项目需持有资质证书开展）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>浙江省杭州市下沙高教园区</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>任奎</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政适当补助 （财政适当补助）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>201927.92万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>浙江省人民政府</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2026年08月10日 至 2027年03月14日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广东梅州职业技术学院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新疆大学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白银矿冶职业技术学院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C72E218F9E5FFD4ED6FFCDF8AF2408A7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>江苏省连云港中等专业学校（连云港市旅游学校、连云港市高级技工学校）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12320700468052383C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>贯彻落实国家中等职业教育方针和民族政策，开展中等职业教育培训，实施素质教育，培养高技能人才；落实民族班办学方针、政策，促进职业教育发展和民族团结。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>江苏省连云港市海州区云台山风景区振华路2号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李大勇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>差额补贴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16536万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>连云港市教育局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2023年12月20日 至 2028年12月20日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12441400MB2D828492</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>06C641FBD834F230C18534E1FC6A2D9C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>承担普通高、中等职业教育和成人学历教育；承担各类继续教育、职业技能培训和鉴定；开展科学研究和社会服务工作；开展国内外、校际教育合作与学术交流。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梅州市梅江区学院路15号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>董芳远</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助 （财政核补）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>25000万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梅州市人民政府</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2026年07月29日 至 2031年07月28日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12650000457601471G</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B36FE3EF394676BF4EDB48385D3CC53D</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>培养高等学历人才，促进科技文化发展。哲学、理学、工学、管理学、法学、文学、历史学等综合类大专、本科、硕士研究生、博士研究生学历教育 博士后培养 相关科学研究、继续教育、专业培训、学术交流等社会服务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>乌鲁木齐市天山区胜利路666号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>马新宾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助 （差额拨款）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>206777万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新疆维吾尔自治区人民政府</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2023年09月06日 至 2028年09月05日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12620400665441476E</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4B09D47326216AFEA6F9A93E12014A58</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>以就业为导向，服务地方经济为目标，培养合格的高等职业技术人才。实施普通高等职业教育和技工教育，开展成人高等教育，积极拓展社会培训和服务功能。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白银市白银区南环路1号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>师永波</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>70175万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白银市教育局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2022年04月22日 至 2027年04月22日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>河北工业大学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>121300004017050446</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4BF5CF264AC2535E437DDE72D57D360B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高等教育及科学研究。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>天津市北辰区双口镇西平道5340号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王利民</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>247493万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2024年12月31日 至 2029年12月30日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ABA98B9BC286D6957C4A29991736A24A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -531,6 +299,86 @@
   </si>
   <si>
     <t>自 2025年02月21日 至 2030年02月20日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙川县福利院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>封开县福利院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12441622456981927F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2F25E9B3DF30F77560E8E29C583EEB76</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承担社会公益性职能，提供收养服务，弘扬救助精神；全心全意为供养、代养人员建立平等、团结、友爱互助的社会主义人际关系，负责收养社会三无老人、残疾老人社会福利事务。负责收养入住的全县孤老重点优抚对象的生活、医疗、管理与服务工作；负责城镇三无老人的收养；提供老人自愿有偿代养服务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广东省龙川县义都镇星光村</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈智宏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （财政补助二类）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>156万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙川县民政局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年06月16日 至 2031年06月15日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12441225070255594J</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4A626D2D8E918E99A4F23EB867EAE2D0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收养社会弃婴（儿）和对残疾儿童进行矫正教育，为老年人、残疾人、孤儿和弃婴等特殊群体提供集中居住、生活照料和康复教育的机构。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>封开县江口街道广信四路</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聂艮华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （财政补助一类）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>封开县民政局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2022年02月24日 至 2027年02月23日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -916,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -969,34 +817,34 @@
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>11</v>
@@ -1004,34 +852,34 @@
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="G3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>11</v>
@@ -1039,34 +887,34 @@
     </row>
     <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>11</v>
@@ -1074,34 +922,34 @@
     </row>
     <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>11</v>
@@ -1109,34 +957,34 @@
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="I6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>11</v>
@@ -1144,34 +992,34 @@
     </row>
     <row r="7" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>11</v>
@@ -1179,34 +1027,34 @@
     </row>
     <row r="8" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>11</v>
@@ -1214,176 +1062,36 @@
     </row>
     <row r="9" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="K9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="K13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
